--- a/ExcelTool/LubanTools/DataTables/Datas/TutorialData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/TutorialData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D654BB9-1F00-4C43-8B7C-0E89AD3CB40F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6454DA1-C346-4E16-9F80-3C5A74914AFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4450" yWindow="2240" windowWidth="44100" windowHeight="18570" xr2:uid="{077F3F2B-6DD6-405A-B7D5-A78214FFC6D2}"/>
+    <workbookView xWindow="-15350" yWindow="9360" windowWidth="44100" windowHeight="18570" xr2:uid="{077F3F2B-6DD6-405A-B7D5-A78214FFC6D2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -161,12 +161,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,6 +507,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40115CB8-B752-45FD-BCFC-A8939664B658}">
   <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="3" max="3" width="30.83203125" customWidth="1"/>
+    <col min="4" max="4" width="38.4140625" customWidth="1"/>
+    <col min="5" max="5" width="38.83203125" customWidth="1"/>
+    <col min="6" max="6" width="20.58203125" customWidth="1"/>
+    <col min="7" max="7" width="24.5" customWidth="1"/>
+    <col min="8" max="8" width="53.25" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
@@ -584,7 +595,7 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="B4">
+      <c r="B4" s="2">
         <v>1001</v>
       </c>
       <c r="C4" s="1" t="s">
